--- a/artfynd/A 44284-2024 artfynd.xlsx
+++ b/artfynd/A 44284-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121223059</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>121223402</v>
       </c>
       <c r="B3" t="n">
-        <v>78243</v>
+        <v>78246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>121247990</v>
       </c>
       <c r="B4" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44284-2024 artfynd.xlsx
+++ b/artfynd/A 44284-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121223059</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>121223402</v>
       </c>
       <c r="B3" t="n">
-        <v>78246</v>
+        <v>78249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>121247990</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44284-2024 artfynd.xlsx
+++ b/artfynd/A 44284-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121223402</v>
+        <v>121247990</v>
       </c>
       <c r="B3" t="n">
-        <v>78249</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,38 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,7 +839,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618985</v>
+        <v>618986</v>
       </c>
       <c r="R3" t="n">
         <v>6662599</v>
@@ -901,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På lämnad rotände. Även vedskivlav.</t>
+          <t>Även dvärgbägarlav på gammal lämnad rotände tallved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247990</v>
+        <v>121223402</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>78249</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,26 +933,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618986</v>
+        <v>618985</v>
       </c>
       <c r="R4" t="n">
         <v>6662599</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Även dvärgbägarlav på gammal lämnad rotände tallved.</t>
+          <t>På lämnad rotände. Även vedskivlav.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44284-2024 artfynd.xlsx
+++ b/artfynd/A 44284-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121223059</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247990</v>
+        <v>121223402</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>78252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +812,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,7 +851,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618986</v>
+        <v>618985</v>
       </c>
       <c r="R3" t="n">
         <v>6662599</v>
@@ -889,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Även dvärgbägarlav på gammal lämnad rotände tallved.</t>
+          <t>På lämnad rotände. Även vedskivlav.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121223402</v>
+        <v>121247990</v>
       </c>
       <c r="B4" t="n">
-        <v>78249</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,38 +945,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618985</v>
+        <v>618986</v>
       </c>
       <c r="R4" t="n">
         <v>6662599</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På lämnad rotände. Även vedskivlav.</t>
+          <t>Även dvärgbägarlav på gammal lämnad rotände tallved.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44284-2024 artfynd.xlsx
+++ b/artfynd/A 44284-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121223402</v>
+        <v>121247990</v>
       </c>
       <c r="B3" t="n">
-        <v>78252</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,38 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,7 +839,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618985</v>
+        <v>618986</v>
       </c>
       <c r="R3" t="n">
         <v>6662599</v>
@@ -901,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På lämnad rotände. Även vedskivlav.</t>
+          <t>Även dvärgbägarlav på gammal lämnad rotände tallved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247990</v>
+        <v>121223402</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>78252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,26 +933,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618986</v>
+        <v>618985</v>
       </c>
       <c r="R4" t="n">
         <v>6662599</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Även dvärgbägarlav på gammal lämnad rotände tallved.</t>
+          <t>På lämnad rotände. Även vedskivlav.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44284-2024 artfynd.xlsx
+++ b/artfynd/A 44284-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121223059</v>
       </c>
       <c r="B2" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>121247990</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>121223402</v>
       </c>
       <c r="B4" t="n">
-        <v>78252</v>
+        <v>78253</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44284-2024 artfynd.xlsx
+++ b/artfynd/A 44284-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121223059</v>
       </c>
       <c r="B2" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>121247990</v>
       </c>
       <c r="B3" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>121223402</v>
       </c>
       <c r="B4" t="n">
-        <v>78253</v>
+        <v>78254</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44284-2024 artfynd.xlsx
+++ b/artfynd/A 44284-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247990</v>
+        <v>121223402</v>
       </c>
       <c r="B3" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +812,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,7 +851,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618986</v>
+        <v>618985</v>
       </c>
       <c r="R3" t="n">
         <v>6662599</v>
@@ -889,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Även dvärgbägarlav på gammal lämnad rotände tallved.</t>
+          <t>På lämnad rotände. Även vedskivlav.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121223402</v>
+        <v>121247990</v>
       </c>
       <c r="B4" t="n">
-        <v>78254</v>
+        <v>79227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,38 +945,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618985</v>
+        <v>618986</v>
       </c>
       <c r="R4" t="n">
         <v>6662599</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På lämnad rotände. Även vedskivlav.</t>
+          <t>Även dvärgbägarlav på gammal lämnad rotände tallved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
